--- a/data/attendance/ANNEX_كحال_علوم_علمي_1.xlsx
+++ b/data/attendance/ANNEX_كحال_علوم_علمي_1.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:252a1438-7e35-43f4-afd1-a377096caf46</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:68d202e3-acdf-44a7-92f3-07c6a299a4f1</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a7337492-9cc9-4b7a-ad3c-7dd954caf817</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:dd35d9fe-24d8-4041-8674-1d6b7c2d016b</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:8ca953f0-962a-4ba9-a0f6-6dfa8c6a69fa</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b4c3e7bb-b0fe-4353-9b65-9f564dc0115a</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:833eafa1-2fa0-4c83-b19c-d17067712947</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6c375ce9-117e-4ec4-802d-6df890e1df21</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7ae7c73b-2712-4e48-beaa-634ceab348ca</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0cfe0815-027f-4666-b86f-bed26b11e38f</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:24c3d709-2613-44aa-8502-c0bdd1904474</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:632f0136-63c1-4b2f-9615-10c0b347987e</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6f03d040-46a2-44a1-9f42-0048ec599056</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:740ab762-55bf-4de7-ac4c-5dde6facc7d0</t>
         </r>
       </text>
@@ -219,112 +118,63 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:b694ed9d-ea55-4048-a284-9463635483b9</t>
+          <t>student_id:8be62056-c7cc-429f-aa94-eb3c945047d1</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:8be62056-c7cc-429f-aa94-eb3c945047d1</t>
+          <t>student_id:8f0a7b17-7789-4b01-8350-f8ecf65527f9</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:8f0a7b17-7789-4b01-8350-f8ecf65527f9</t>
+          <t>student_id:6d694151-35a9-4d6d-a593-b932539c954e</t>
         </r>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:6d694151-35a9-4d6d-a593-b932539c954e</t>
+          <t>student_id:403b43f6-ba27-46ff-800e-c1145a44c2b9</t>
         </r>
       </text>
     </comment>
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:403b43f6-ba27-46ff-800e-c1145a44c2b9</t>
+          <t>student_id:c15597b8-2c0c-4d0e-af39-0bb27721d1ec</t>
         </r>
       </text>
     </comment>
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:c15597b8-2c0c-4d0e-af39-0bb27721d1ec</t>
+          <t>student_id:a8c96b3d-7161-4ad9-851c-a32cff277ace</t>
         </r>
       </text>
     </comment>
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:a8c96b3d-7161-4ad9-851c-a32cff277ace</t>
+          <t>student_id:5c9fc292-1307-4ccc-a04a-036d34a8384f</t>
         </r>
       </text>
     </comment>
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:5c9fc292-1307-4ccc-a04a-036d34a8384f</t>
+          <t>student_id:dc7970ba-b376-42e4-9249-e7d9c865c8c5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0">
+      <text>
+        <r>
+          <t>student_id:488aec9c-65d4-4924-9bee-7b4ee49150db</t>
         </r>
       </text>
     </comment>
@@ -333,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>كحال علوم علمي 1  |  ANNEX  |  BAC  |  كحال لمياء</t>
   </si>
@@ -347,6 +197,9 @@
     <t>has_books=true</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -371,7 +224,14 @@
     <t>25/09/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 1
+ت 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 2
 ت 1</t>
   </si>
   <si>
@@ -422,10 +282,7 @@
     <t>مشيروف سيرين نورهان</t>
   </si>
   <si>
-    <t>مخبي ريم</t>
-  </si>
-  <si>
-    <t>عناني عبد الرؤوف</t>
+    <t>موخبي ريم</t>
   </si>
   <si>
     <t>بن مشير فؤاد</t>
@@ -449,6 +306,12 @@
     <t>طالبي محمد أيوب</t>
   </si>
   <si>
+    <t>بن سباعي رقية</t>
+  </si>
+  <si>
+    <t>صحراوي شهاب</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -476,7 +339,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -498,40 +364,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -634,7 +493,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -995,15 +854,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,8 +882,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1034,10 +894,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1077,86 +940,92 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>9</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
@@ -1191,25 +1060,28 @@
       <c r="Q5" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>18</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
@@ -1244,25 +1116,28 @@
       <c r="Q6" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>38</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
@@ -1297,19 +1172,22 @@
       <c r="Q7" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>55</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="12">
         <v>0</v>
       </c>
       <c r="D8" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
@@ -1350,25 +1228,28 @@
       <c r="Q8" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>97</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1403,13 +1284,16 @@
       <c r="Q9" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>351</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" s="12">
         <v>0</v>
@@ -1421,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -1456,19 +1340,22 @@
       <c r="Q10" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>399</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
@@ -1509,25 +1396,28 @@
       <c r="Q11" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>400</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="12">
         <v>0</v>
       </c>
       <c r="D12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -1562,13 +1452,16 @@
       <c r="Q12" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>401</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -1615,25 +1508,28 @@
       <c r="Q13" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>402</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
@@ -1668,25 +1564,28 @@
       <c r="Q14" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>403</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
       </c>
       <c r="D15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10">
         <v>0</v>
@@ -1721,25 +1620,28 @@
       <c r="Q15" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>404</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" s="12">
         <v>0</v>
       </c>
       <c r="D16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0</v>
@@ -1774,25 +1676,28 @@
       <c r="Q16" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>405</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10">
         <v>0</v>
@@ -1827,25 +1732,28 @@
       <c r="Q17" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>406</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="12">
         <v>0</v>
@@ -1880,25 +1788,28 @@
       <c r="Q18" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="10">
         <v>0</v>
@@ -1933,25 +1844,28 @@
       <c r="Q19" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="12">
         <v>0</v>
@@ -1986,25 +1900,28 @@
       <c r="Q20" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="10">
         <v>0</v>
@@ -2039,25 +1956,28 @@
       <c r="Q21" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C22" s="12">
         <v>0</v>
       </c>
       <c r="D22" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
@@ -2092,25 +2012,28 @@
       <c r="Q22" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
       </c>
       <c r="D23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="10">
         <v>0</v>
@@ -2145,13 +2068,16 @@
       <c r="Q23" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C24" s="12">
         <v>0</v>
@@ -2160,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="12">
         <v>0</v>
@@ -2198,13 +2124,16 @@
       <c r="Q24" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C25" s="10">
         <v>0</v>
@@ -2216,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="10">
         <v>0</v>
@@ -2251,13 +2180,16 @@
       <c r="Q25" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>414</v>
+        <v>865</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C26" s="12">
         <v>0</v>
@@ -2269,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="12">
         <v>0</v>
@@ -2302,16 +2234,75 @@
         <v>0</v>
       </c>
       <c r="Q26" s="11">
+        <v>0</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>866</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0</v>
+      </c>
+      <c r="O27" s="11">
+        <v>0</v>
+      </c>
+      <c r="P27" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>0</v>
+      </c>
+      <c r="R27" s="11">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2321,89 +2312,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>